--- a/flow_data.xlsx
+++ b/flow_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rettigod\VS Projects\CHE411\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{155D71C7-88E3-4CB1-8C73-7C37D496D62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2506571E-C52B-4102-9998-274198BDA1BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{F0F2802D-E2C9-42F9-BB95-1D4D3BED6308}"/>
+    <workbookView xWindow="3384" yWindow="3384" windowWidth="17280" windowHeight="9960" xr2:uid="{F0F2802D-E2C9-42F9-BB95-1D4D3BED6308}"/>
   </bookViews>
   <sheets>
     <sheet name="4gpm" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="15">
   <si>
     <t>cold_side</t>
   </si>
@@ -77,6 +77,12 @@
   </si>
   <si>
     <t>avg_surf_temp</t>
+  </si>
+  <si>
+    <t>rel_hum</t>
+  </si>
+  <si>
+    <t>T_ambient(F)</t>
   </si>
 </sst>
 </file>
@@ -100,7 +106,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -123,14 +129,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,7 +506,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FCA5C00-E037-4A8A-BCCB-63CCC9CF2CCF}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -474,9 +515,10 @@
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -492,83 +534,70 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>16.55</v>
-      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
-        <v>25.57</v>
-      </c>
+      <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1">
-        <v>25.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>20.43</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
-        <v>23.83</v>
-      </c>
+      <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>2</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
-        <v>2</v>
-      </c>
+      <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>4</v>
-      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
-        <v>9.6</v>
-      </c>
+      <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -577,7 +606,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9A43BAA-FD75-412E-A7E9-F8DE6F170CD3}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -586,9 +615,11 @@
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,89 +629,76 @@
       <c r="C1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>16.850000000000001</v>
-      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1">
-        <v>25.31</v>
-      </c>
+      <c r="D2" s="2"/>
       <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="1">
-        <v>25.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>19.739999999999998</v>
-      </c>
+      <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1">
-        <v>23.36</v>
-      </c>
+      <c r="D3" s="2"/>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>0</v>
-      </c>
+      <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
+      <c r="D4" s="2"/>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>6</v>
-      </c>
+      <c r="B5" s="1"/>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="1">
-        <v>9.6</v>
-      </c>
+      <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -689,7 +707,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7182DDEE-97BA-4390-8ED2-C78F48C9E592}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
@@ -698,9 +716,11 @@
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -716,11 +736,17 @@
       <c r="E1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -733,8 +759,10 @@
         <v>6</v>
       </c>
       <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -746,9 +774,8 @@
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -760,9 +787,8 @@
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
@@ -774,7 +800,6 @@
       <c r="E5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
